--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260914.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260914.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>77,907</t>
+          <t>77,107</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.22%</t>
+          <t>10.84%</t>
         </is>
       </c>
     </row>
@@ -633,56 +633,56 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>32,296</t>
+          <t>31,796</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.46%</t>
+          <t>9.95%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>VRT US</t>
+          <t>PWR US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>維諦技術控股公司</t>
+          <t>廣達服務公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>90,525</t>
+          <t>35,255</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.88%</t>
+          <t>7.84%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>PWR US</t>
+          <t>VRT US</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>廣達服務公司</t>
+          <t>維諦技術控股公司</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>35,555</t>
+          <t>89,525</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.83%</t>
+          <t>7.60%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>195,556</t>
+          <t>193,356</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.45%</t>
+          <t>5.65%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>49,095</t>
+          <t>48,495</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.58%</t>
+          <t>4.46%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>103,991</t>
+          <t>102,791</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.20%</t>
+          <t>4.38%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>112,766</t>
+          <t>111,466</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.47%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>59,059</t>
+          <t>58,359</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>19,379</t>
+          <t>19,179</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>3.04%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>117,283</t>
+          <t>115,983</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>54,327</t>
+          <t>53,727</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.35%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>22,531</t>
+          <t>22,331</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>136,601</t>
+          <t>135,001</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.06%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>24,304</t>
+          <t>24,104</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>62,403</t>
+          <t>61,703</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -963,56 +963,56 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>36,780</t>
+          <t>36,480</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>PEG US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>大眾服務企業集團公司</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>49,836</t>
+          <t>76,301</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>PEG US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>大眾服務企業集團公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>77,101</t>
+          <t>49,236</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>95,263</t>
+          <t>94,163</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>32,510</t>
+          <t>32,210</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
@@ -1073,29 +1073,29 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>50,160</t>
+          <t>49,560</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>22,258</t>
+          <t>30,145</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,22 +1107,22 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>30,445</t>
+          <t>22,058</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1139,56 +1139,56 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>47,127</t>
+          <t>46,627</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>27,569</t>
+          <t>50,710</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>51,310</t>
+          <t>27,269</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>20,709</t>
+          <t>20,509</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>11,337</t>
+          <t>11,237</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,39 +1239,39 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>9,004</t>
+          <t>74,374</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>75,174</t>
+          <t>30,014</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,66 +1283,66 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>202609ESU6</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>小型S＆P 500股價指數</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>30,314</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>13,252</t>
+          <t>8,904</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>202609ESU6</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>小型S＆P 500股價指數</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13,152</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1359,56 +1359,56 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>30,691</t>
+          <t>30,391</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>4,921</t>
+          <t>144,545</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>146,245</t>
+          <t>4,921</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>10,646</t>
+          <t>10,546</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>25,781</t>
+          <t>25,581</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -1469,51 +1469,51 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>43,583</t>
+          <t>43,083</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>PNW US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>皮那可資本公司</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>13,424</t>
+          <t>15,927</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>PNW US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>皮那可資本公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>16,127</t>
+          <t>13,324</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>94,702</t>
+          <t>93,602</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>6,827</t>
+          <t>6,727</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>5,878</t>
+          <t>5,778</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>23,519</t>
+          <t>23,319</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>8,021</t>
+          <t>7,921</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>18,453</t>
+          <t>18,253</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>38,261</t>
+          <t>37,861</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1729,7 +1729,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>129,061,564</t>
+          <t>123,064,872</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
